--- a/upload/renuncias_concedidas.xlsx
+++ b/upload/renuncias_concedidas.xlsx
@@ -9,11 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8730"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$F$67</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="71">
   <si>
     <t>ano</t>
   </si>
@@ -39,9 +42,6 @@
   </si>
   <si>
     <t>Isenção</t>
-  </si>
-  <si>
-    <t>Decreto nº 48.968/2024</t>
   </si>
   <si>
     <r>
@@ -324,6 +324,18 @@
   <si>
     <t>montante_perdas</t>
   </si>
+  <si>
+    <t>Lei nº 25.144/25 e Resolução conjunta SEF/AGE Nº 5.942/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decreto nº 48.968/2024 e Decreto nº 49.157/2025 </t>
+  </si>
+  <si>
+    <t>Lei nº 25.626/25</t>
+  </si>
+  <si>
+    <t>Dec. 46.817/2015</t>
+  </si>
 </sst>
 </file>
 
@@ -331,7 +343,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -404,7 +416,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -427,6 +439,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -436,7 +461,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -454,22 +479,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -488,12 +504,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -509,6 +519,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -795,1291 +811,1360 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F64"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="7" width="43.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="23" t="s">
         <v>66</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2025</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
+      <c r="B2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="5">
-        <v>4735811.9738734104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18625980.316613324</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2025</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="F3" s="5">
-        <v>14378052.731433598</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+        <v>3218257.2800000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2025</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="8">
-        <v>9247117053.8943691</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="5">
+        <v>162781175.99140295</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="8">
-        <v>142128494.59440133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="5">
+        <v>24267184.940000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="8">
-        <v>465782586.69000846</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5">
+        <v>19598189942.468018</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="1" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1316816313.8605902</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5">
+        <v>383288932.74021184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="8">
-        <v>65589734.01819995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1814517885.2100172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>2025</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="8">
-        <v>4027212.4600000074</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2919830387.4699965</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2025</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="5">
+        <v>105836071.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="5">
+        <v>954155.77999998385</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="5">
+        <v>11015092.3799999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="8">
-        <v>1095492.6300000024</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="27" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="5">
-        <v>133571864.62553526</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="5">
-        <v>1757704760.3699965</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="F13" s="5">
-        <v>577329.27999999968</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+        <v>1923750.9200000088</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>26</v>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F14" s="5">
-        <v>17187681416.083221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+        <v>133571864.62553526</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>2024</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>19</v>
+      <c r="B15" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>27</v>
+      <c r="D15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F15" s="5">
-        <v>276368820.47937691</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+        <v>1757704760.3699965</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>2024</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>28</v>
+      <c r="B16" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F16" s="5">
-        <v>184214726.71999961</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>577329.27999999968</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>2024</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>13</v>
+      <c r="E17" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F17" s="5">
-        <v>2488932407.0999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>17187681416.083221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="51" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2024</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>13</v>
+      <c r="E18" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F18" s="5">
-        <v>124290064.81999563</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>276368820.47937691</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>2024</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="F19" s="5">
-        <v>10136457.880000019</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>184214726.71999961</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>2024</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="5">
+        <v>2488932407.0999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="5">
+        <v>124290064.81999563</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="5">
+        <v>10136457.880000019</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="5">
+      <c r="F23" s="5">
         <v>2139675.6399999936</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="27" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="5">
-        <v>25337059.720000003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="5">
-        <v>37623944.3819272</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F23" s="5">
-        <v>15730276.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>2023</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F24" s="5">
-        <v>15317977706.218988</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>25337059.720000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>2023</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>19</v>
+      <c r="B25" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F25" s="5">
-        <v>274600804.97459996</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+        <v>37623944.3819272</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>2023</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>19</v>
+      <c r="B26" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>35</v>
+      <c r="D26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="F26" s="5">
-        <v>364431430.86000448</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15730276.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>2023</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="F27" s="5">
-        <v>2735548422.1651545</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15317977706.218988</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2023</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>13</v>
+      <c r="E28" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="F28" s="5">
-        <v>166594809.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>274600804.97459996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2023</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>36</v>
+        <v>8</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="F29" s="5">
-        <v>8368465.4200000726</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>364431430.86000448</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2023</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="5">
+        <v>2735548422.1651545</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="5">
+        <v>166594809.37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" s="5">
+        <v>8368465.4200000726</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="5">
+      <c r="F33" s="5">
         <v>2251016.2099999995</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="5">
-        <v>24976575.540023353</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="5">
-        <v>14624489</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="5">
-        <v>4782976</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" s="1" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>2022</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>34</v>
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F34" s="5">
-        <v>12716864156.757729</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>24976575.540023353</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>2022</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>19</v>
+      <c r="B35" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>30</v>
+      <c r="D35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="F35" s="5">
-        <v>230582188.99700007</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" s="1" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+        <v>14624489</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>2022</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>19</v>
+      <c r="B36" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="F36" s="5">
-        <v>978426577</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>4782976</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" s="1" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>2022</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="F37" s="5">
-        <v>1356593269</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>12716864156.757729</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>2022</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>13</v>
+      <c r="E38" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="F38" s="5">
-        <v>48101596</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>230582188.99700007</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" s="1" customFormat="1" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>2022</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>42</v>
+        <v>8</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="F39" s="5">
-        <v>197571</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>978426577</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>2022</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>43</v>
+        <v>11</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F40" s="5">
-        <v>6257314</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1356593269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2022</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="5">
+        <v>48101596</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" s="5">
+        <v>197571</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="5">
+        <v>6257314</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" s="18">
+      <c r="F44" s="15">
         <v>2201661</v>
       </c>
     </row>
-    <row r="42" spans="1:6" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F42" s="12">
-        <v>31201545.827456355</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F43" s="12">
-        <v>2009047661.3300004</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="12">
-        <v>7892333.5000000037</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" s="1" customFormat="1" ht="27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>2021</v>
       </c>
-      <c r="B45" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F45" s="12">
-        <v>28372014.919999991</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F45" s="9">
+        <v>31201545.827456355</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>2021</v>
       </c>
-      <c r="B46" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F46" s="12">
-        <v>910754.65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" s="1" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B46" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" s="9">
+        <v>2009047661.3300004</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>2021</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F47" s="12">
-        <v>11367601454.264412</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" s="1" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B47" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" s="9">
+        <v>7892333.5000000037</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>2021</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F48" s="12">
-        <v>76901070.261982694</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="9">
+        <v>28372014.919999991</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>2021</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F49" s="12">
-        <v>619405021.88000083</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B49" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" s="9">
+        <v>910754.65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="1" customFormat="1" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>2021</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>1</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="12">
-        <v>886942414.74968684</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F50" s="9">
+        <v>11367601454.264412</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="1" customFormat="1" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>2021</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E51" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="12">
-        <v>47809190.000000633</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F51" s="9">
+        <v>76901070.261982694</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>2021</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F52" s="12">
-        <v>3966191.7300000116</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F52" s="9">
+        <v>619405021.88000083</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" s="1" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>2021</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F53" s="12">
-        <v>1631937.609999998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="9">
+        <v>886942414.74968684</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>2021</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="9">
+        <v>47809190.000000633</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" s="9">
+        <v>3966191.7300000116</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F56" s="9">
+        <v>1631937.609999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C54" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="26" t="s">
+      <c r="E57" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E54" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F54" s="15">
+      <c r="F57" s="12">
         <v>1239950649.7350979</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="27" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F55" s="5">
-        <v>16641994.372726467</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F56" s="12">
-        <v>7157748739.5117693</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F57" s="12">
-        <v>75459846.163199961</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>2020</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F58" s="12">
-        <v>527774369.61999965</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="E58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F58" s="5">
+        <v>16641994.372726467</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>2020</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E59" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="12">
-        <v>1044423458.9000002</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F59" s="9">
+        <v>7157748739.5117693</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>2020</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C60" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E60" s="23"/>
-      <c r="F60" s="12">
-        <v>79838644.000000149</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E60" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F60" s="9">
+        <v>75459846.163199961</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>2020</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F61" s="12">
-        <v>3839325.1700000102</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F61" s="9">
+        <v>527774369.61999965</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>2020</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C62" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F62" s="12">
-        <v>634613.07999999914</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="9">
+        <v>1044423458.9000002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>2020</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F63" s="17">
-        <v>7126028512.5727797</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E63" s="18"/>
+      <c r="F63" s="9">
+        <v>79838644.000000149</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>2020</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F64" s="9">
+        <v>3839325.1700000102</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F65" s="9">
+        <v>634613.07999999914</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F66" s="14">
+        <v>7126028512.5727797</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F64" s="17">
+      <c r="E67" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F67" s="14">
         <v>1021369713.2659395</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F67">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="2025"/>
+      </filters>
+    </filterColumn>
+    <sortState ref="A2:F10">
+      <sortCondition ref="B1:B64"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
